--- a/Excel9to10/Advance Descriptive Analytics.xlsx
+++ b/Excel9to10/Advance Descriptive Analytics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiten\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0035C-ACEE-40D6-991B-0D603531FFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7C9A7F-3D09-4D61-A028-9566696ACC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9EBBF17A-A1CB-4F22-9D4F-1F4F44E8488B}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="209">
   <si>
     <t>Emp No</t>
   </si>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>Hunter Glantz</t>
-  </si>
-  <si>
-    <t>Hunter Lopez</t>
-  </si>
-  <si>
-    <t>Ionia McGrath</t>
   </si>
   <si>
     <t>Irene Maddox</t>
@@ -2018,7 +2012,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2029,7 +2023,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D6" s="4">
         <v>26988</v>
@@ -2039,10 +2033,10 @@
       </c>
       <c r="F6" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -2055,7 +2049,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D7" s="4">
         <v>30426</v>
@@ -2071,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2082,7 +2076,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D8" s="4">
         <v>25935</v>
@@ -2098,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2109,7 +2103,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D9" s="4">
         <v>27741</v>
@@ -2136,7 +2130,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D10" s="4">
         <v>34033</v>
@@ -2163,7 +2157,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D11" s="4">
         <v>32225</v>
@@ -2190,7 +2184,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D12" s="4">
         <v>31029</v>
@@ -2217,7 +2211,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D13" s="4">
         <v>28036</v>
@@ -2239,7 +2233,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D14" s="4">
         <v>33648</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="F14" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -2260,7 +2254,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D15" s="4">
         <v>29657</v>
@@ -2278,10 +2272,10 @@
         <v>730727</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D16" s="4">
         <v>27766</v>
@@ -2294,11 +2288,11 @@
         <v>NO</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -2306,10 +2300,10 @@
         <v>741587</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D17" s="4">
         <v>35336</v>
@@ -2324,13 +2318,13 @@
       <c r="H17">
         <v>1</v>
       </c>
-      <c r="I17" t="e">
+      <c r="I17" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J17,Data[Date of Admission]))</f>
-        <v>#N/A</v>
+        <v>Hunter Glantz</v>
       </c>
       <c r="J17" s="1">
         <f>SMALL(Data[Date of Admission],H17)</f>
-        <v>26299</v>
+        <v>26751</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -2338,10 +2332,10 @@
         <v>823715</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D18" s="4">
         <v>35352</v>
@@ -2356,13 +2350,13 @@
       <c r="H18">
         <v>2</v>
       </c>
-      <c r="I18" t="e">
+      <c r="I18" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J18,Data[Date of Admission]))</f>
-        <v>#N/A</v>
+        <v>Irene Maddox</v>
       </c>
       <c r="J18" s="1">
         <f>SMALL(Data[Date of Admission],H18)</f>
-        <v>26665</v>
+        <v>27158</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -2370,10 +2364,10 @@
         <v>656271</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D19" s="4">
         <v>33187</v>
@@ -2383,18 +2377,18 @@
       </c>
       <c r="F19" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H19">
         <v>3</v>
       </c>
       <c r="I19" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J19,Data[Date of Admission]))</f>
-        <v>Hunter Glantz</v>
+        <v>Ivan Gibson</v>
       </c>
       <c r="J19" s="1">
         <f>SMALL(Data[Date of Admission],H19)</f>
-        <v>26751</v>
+        <v>27395</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -2402,10 +2396,10 @@
         <v>633456</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D20" s="4">
         <v>34377</v>
@@ -2415,18 +2409,18 @@
       </c>
       <c r="F20" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H20">
         <v>4</v>
       </c>
       <c r="I20" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J20,Data[Date of Admission]))</f>
-        <v>Irene Maddox</v>
+        <v>Ivan Liston</v>
       </c>
       <c r="J20" s="1">
         <f>SMALL(Data[Date of Admission],H20)</f>
-        <v>27158</v>
+        <v>28120</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -2434,10 +2428,10 @@
         <v>620254</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D21" s="4">
         <v>36045</v>
@@ -2454,11 +2448,11 @@
       </c>
       <c r="I21" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J21,Data[Date of Admission]))</f>
-        <v>Ivan Gibson</v>
+        <v>Jack Garza</v>
       </c>
       <c r="J21" s="1">
         <f>SMALL(Data[Date of Admission],H21)</f>
-        <v>27395</v>
+        <v>28342</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -2466,10 +2460,10 @@
         <v>612222</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D22" s="4">
         <v>35485</v>
@@ -2479,18 +2473,18 @@
       </c>
       <c r="F22" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J22,Data[Date of Admission]))</f>
-        <v>Ivan Liston</v>
+        <v>Jack O'Briant</v>
       </c>
       <c r="J22" s="1">
         <f>SMALL(Data[Date of Admission],H22)</f>
-        <v>28120</v>
+        <v>28795</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2498,10 +2492,10 @@
         <v>613597</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D23" s="4">
         <v>30960</v>
@@ -2518,11 +2512,11 @@
       </c>
       <c r="I23" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J23,Data[Date of Admission]))</f>
-        <v>Jack Garza</v>
+        <v>James Galang</v>
       </c>
       <c r="J23" s="1">
         <f>SMALL(Data[Date of Admission],H23)</f>
-        <v>28342</v>
+        <v>29544</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -2533,7 +2527,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D24" s="4">
         <v>36211</v>
@@ -2543,18 +2537,18 @@
       </c>
       <c r="F24" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H24">
         <v>8</v>
       </c>
       <c r="I24" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J24,Data[Date of Admission]))</f>
-        <v>Jack O'Briant</v>
+        <v>James Lanier</v>
       </c>
       <c r="J24" s="1">
         <f>SMALL(Data[Date of Admission],H24)</f>
-        <v>28795</v>
+        <v>29679</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -2565,7 +2559,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D25" s="4">
         <v>31594</v>
@@ -2582,11 +2576,11 @@
       </c>
       <c r="I25" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J25,Data[Date of Admission]))</f>
-        <v>James Galang</v>
+        <v>Jamie Frazer</v>
       </c>
       <c r="J25" s="1">
         <f>SMALL(Data[Date of Admission],H25)</f>
-        <v>29544</v>
+        <v>29888</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -2597,7 +2591,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D26" s="4">
         <v>31831</v>
@@ -2607,18 +2601,18 @@
       </c>
       <c r="F26" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H26">
         <v>10</v>
       </c>
       <c r="I26" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J26,Data[Date of Admission]))</f>
-        <v>James Lanier</v>
+        <v>Jamie Kunitz</v>
       </c>
       <c r="J26" s="1">
         <f>SMALL(Data[Date of Admission],H26)</f>
-        <v>29679</v>
+        <v>29932</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -2644,47 +2638,21 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
-        <v>783507</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="4">
-        <v>20688</v>
-      </c>
-      <c r="E28" s="11">
-        <v>26299</v>
-      </c>
-      <c r="F28" s="6" t="str">
-        <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
-      </c>
+      <c r="A28" s="10"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="6"/>
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
-        <v>624408</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="4">
-        <v>21151</v>
-      </c>
-      <c r="E29" s="11">
-        <v>26665</v>
-      </c>
-      <c r="F29" s="6" t="str">
-        <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
-      </c>
+      <c r="A29" s="10"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="6"/>
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -2692,7 +2660,7 @@
         <v>624461</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>14</v>
@@ -2708,11 +2676,11 @@
         <v>NO</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -2720,7 +2688,7 @@
         <v>735223</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -2752,7 +2720,7 @@
         <v>771206</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -2784,7 +2752,7 @@
         <v>774976</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -2797,7 +2765,7 @@
       </c>
       <c r="F33" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H33">
         <v>3</v>
@@ -2816,7 +2784,7 @@
         <v>835503</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2848,7 +2816,7 @@
         <v>802336</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -2880,7 +2848,7 @@
         <v>766045</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2912,7 +2880,7 @@
         <v>621238</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>11</v>
@@ -2944,7 +2912,7 @@
         <v>658088</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>11</v>
@@ -2976,7 +2944,7 @@
         <v>792571</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -3008,7 +2976,7 @@
         <v>821518</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>12</v>
@@ -3021,7 +2989,7 @@
       </c>
       <c r="F40" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H40">
         <v>10</v>
@@ -3040,7 +3008,7 @@
         <v>665693</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>16</v>
@@ -3062,7 +3030,7 @@
         <v>712454</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>16</v>
@@ -3084,7 +3052,7 @@
         <v>707767</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>10</v>
@@ -3106,7 +3074,7 @@
         <v>801566</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>13</v>
@@ -3128,7 +3096,7 @@
         <v>817486</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>13</v>
@@ -3144,11 +3112,11 @@
         <v>NO</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -3156,7 +3124,7 @@
         <v>622391</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>10</v>
@@ -3188,7 +3156,7 @@
         <v>749614</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -3220,7 +3188,7 @@
         <v>624719</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>12</v>
@@ -3252,7 +3220,7 @@
         <v>779841</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>13</v>
@@ -3272,11 +3240,11 @@
       </c>
       <c r="I49" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J49,Data[Date of Birth],0))</f>
-        <v>Hunter Lopez</v>
+        <v>Ross DeVincentis</v>
       </c>
       <c r="J49" s="5">
         <f>SMALL(Data[Date of Birth],H49)</f>
-        <v>20688</v>
+        <v>20775</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -3284,7 +3252,7 @@
         <v>837844</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -3304,11 +3272,11 @@
       </c>
       <c r="I50" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J50,Data[Date of Birth],0))</f>
-        <v>Ross DeVincentis</v>
+        <v>Hunter Glantz</v>
       </c>
       <c r="J50" s="5">
         <f>SMALL(Data[Date of Birth],H50)</f>
-        <v>20775</v>
+        <v>20915</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -3316,7 +3284,7 @@
         <v>753170</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>12</v>
@@ -3336,11 +3304,11 @@
       </c>
       <c r="I51" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J51,Data[Date of Birth],0))</f>
-        <v>Hunter Glantz</v>
+        <v>Ivan Liston</v>
       </c>
       <c r="J51" s="5">
         <f>SMALL(Data[Date of Birth],H51)</f>
-        <v>20915</v>
+        <v>21179</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -3348,7 +3316,7 @@
         <v>655433</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>11</v>
@@ -3361,18 +3329,18 @@
       </c>
       <c r="F52" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H52">
         <v>7</v>
       </c>
       <c r="I52" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J52,Data[Date of Birth],0))</f>
-        <v>Ionia McGrath</v>
+        <v>Irene Maddox</v>
       </c>
       <c r="J52" s="5">
         <f>SMALL(Data[Date of Birth],H52)</f>
-        <v>21151</v>
+        <v>21214</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -3380,7 +3348,7 @@
         <v>669122</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -3400,11 +3368,11 @@
       </c>
       <c r="I53" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J53,Data[Date of Birth],0))</f>
-        <v>Ivan Liston</v>
+        <v>Dean Braden</v>
       </c>
       <c r="J53" s="5">
         <f>SMALL(Data[Date of Birth],H53)</f>
-        <v>21179</v>
+        <v>21398</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -3412,7 +3380,7 @@
         <v>773427</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
@@ -3432,11 +3400,11 @@
       </c>
       <c r="I54" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J54,Data[Date of Birth],0))</f>
-        <v>Irene Maddox</v>
+        <v>Jack O'Briant</v>
       </c>
       <c r="J54" s="5">
         <f>SMALL(Data[Date of Birth],H54)</f>
-        <v>21214</v>
+        <v>21524</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -3444,7 +3412,7 @@
         <v>646283</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>12</v>
@@ -3457,18 +3425,18 @@
       </c>
       <c r="F55" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H55">
         <v>10</v>
       </c>
       <c r="I55" t="str">
         <f>INDEX(Data[Emp Name],MATCH(J55,Data[Date of Birth],0))</f>
-        <v>Dean Braden</v>
+        <v>Jamie Kunitz</v>
       </c>
       <c r="J55" s="5">
         <f>SMALL(Data[Date of Birth],H55)</f>
-        <v>21398</v>
+        <v>21807</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -3476,7 +3444,7 @@
         <v>718778</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>16</v>
@@ -3498,7 +3466,7 @@
         <v>685311</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>13</v>
@@ -3520,7 +3488,7 @@
         <v>840067</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>11</v>
@@ -3542,7 +3510,7 @@
         <v>701146</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>16</v>
@@ -3555,7 +3523,7 @@
       </c>
       <c r="F59" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="J59" s="5"/>
     </row>
@@ -3564,7 +3532,7 @@
         <v>631665</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>10</v>
@@ -3580,11 +3548,11 @@
         <v>NO</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -3592,7 +3560,7 @@
         <v>633397</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3614,7 +3582,7 @@
         <v>780726</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3627,7 +3595,7 @@
       </c>
       <c r="F62" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="J62" s="5"/>
     </row>
@@ -3636,7 +3604,7 @@
         <v>715044</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>10</v>
@@ -3658,7 +3626,7 @@
         <v>660239</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>10</v>
@@ -3680,7 +3648,7 @@
         <v>767280</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>10</v>
@@ -3702,7 +3670,7 @@
         <v>634320</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>16</v>
@@ -3724,7 +3692,7 @@
         <v>833590</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>10</v>
@@ -3746,7 +3714,7 @@
         <v>675037</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>11</v>
@@ -3768,7 +3736,7 @@
         <v>757786</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>16</v>
@@ -3781,7 +3749,7 @@
       </c>
       <c r="F69" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="J69" s="5"/>
     </row>
@@ -3790,7 +3758,7 @@
         <v>762734</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>10</v>
@@ -3812,7 +3780,7 @@
         <v>640992</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>16</v>
@@ -3825,7 +3793,7 @@
       </c>
       <c r="F71" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="J71" s="5"/>
     </row>
@@ -3834,7 +3802,7 @@
         <v>677349</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>13</v>
@@ -3856,7 +3824,7 @@
         <v>644319</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>16</v>
@@ -3878,7 +3846,7 @@
         <v>766049</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>11</v>
@@ -3900,7 +3868,7 @@
         <v>716703</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>13</v>
@@ -3916,11 +3884,11 @@
         <v>NO</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3928,7 +3896,7 @@
         <v>652603</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>12</v>
@@ -3945,7 +3913,7 @@
       </c>
       <c r="H76" t="str" cm="1">
         <f t="array" aca="1" ref="H76:H90" ca="1">_xlfn._xlws.FILTER(Data[Emp Name],Data[BD]="YES")</f>
-        <v>Aaron Bergman</v>
+        <v>Dianna Wilson</v>
       </c>
       <c r="J76">
         <f ca="1">COUNTIF(Data[BD],"YES")</f>
@@ -3957,7 +3925,7 @@
         <v>728401</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>16</v>
@@ -3970,11 +3938,11 @@
       </c>
       <c r="F77" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H77" t="str">
         <f ca="1"/>
-        <v>Susan Vittorini</v>
+        <v>Suzanne McNair</v>
       </c>
       <c r="J77" s="5"/>
     </row>
@@ -3983,7 +3951,7 @@
         <v>777036</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>10</v>
@@ -4000,7 +3968,7 @@
       </c>
       <c r="H78" t="str">
         <f ca="1"/>
-        <v>Ionia McGrath</v>
+        <v>Tamara Chand</v>
       </c>
       <c r="J78" s="5"/>
     </row>
@@ -4009,7 +3977,7 @@
         <v>706249</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -4026,7 +3994,7 @@
       </c>
       <c r="H79" t="str">
         <f ca="1"/>
-        <v>Janet Lee</v>
+        <v>Henry MacAllister</v>
       </c>
       <c r="J79" s="5"/>
     </row>
@@ -4035,7 +4003,7 @@
         <v>837626</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>10</v>
@@ -4052,7 +4020,7 @@
       </c>
       <c r="H80" t="str">
         <f ca="1"/>
-        <v>Matt Connell</v>
+        <v>Hilary Holden</v>
       </c>
       <c r="J80" s="5"/>
     </row>
@@ -4061,7 +4029,7 @@
         <v>745916</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>11</v>
@@ -4078,7 +4046,7 @@
       </c>
       <c r="H81" t="str">
         <f ca="1"/>
-        <v>Matthew Grinstein</v>
+        <v>Jack Garza</v>
       </c>
       <c r="J81" s="5"/>
     </row>
@@ -4087,7 +4055,7 @@
         <v>841887</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>16</v>
@@ -4104,7 +4072,7 @@
       </c>
       <c r="H82" t="str">
         <f ca="1"/>
-        <v>Michael Dominguez</v>
+        <v>Maurice Satty</v>
       </c>
       <c r="J82" s="5"/>
     </row>
@@ -4113,7 +4081,7 @@
         <v>753294</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>12</v>
@@ -4126,11 +4094,11 @@
       </c>
       <c r="F83" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H83" t="str">
         <f ca="1"/>
-        <v>Michael Granlund</v>
+        <v>Max Ludwig</v>
       </c>
       <c r="J83" s="5"/>
     </row>
@@ -4139,7 +4107,7 @@
         <v>704786</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>13</v>
@@ -4156,7 +4124,7 @@
       </c>
       <c r="H84" t="str">
         <f ca="1"/>
-        <v>Michael Stewart</v>
+        <v>Michelle Tran</v>
       </c>
       <c r="J84" s="5"/>
     </row>
@@ -4165,7 +4133,7 @@
         <v>613639</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>12</v>
@@ -4182,7 +4150,7 @@
       </c>
       <c r="H85" t="str">
         <f ca="1"/>
-        <v>Muhammed Yedwab</v>
+        <v>Natalie Fritzler</v>
       </c>
       <c r="J85" s="5"/>
     </row>
@@ -4191,7 +4159,7 @@
         <v>650629</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>16</v>
@@ -4208,7 +4176,7 @@
       </c>
       <c r="H86" t="str">
         <f ca="1"/>
-        <v>Natalie Webber</v>
+        <v>Nick Zandusky</v>
       </c>
       <c r="J86" s="5"/>
     </row>
@@ -4217,7 +4185,7 @@
         <v>768614</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>10</v>
@@ -4234,7 +4202,7 @@
       </c>
       <c r="H87" t="str">
         <f ca="1"/>
-        <v>Robert Barroso</v>
+        <v>Randy Bradley</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
@@ -4242,7 +4210,7 @@
         <v>646103</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>12</v>
@@ -4259,7 +4227,7 @@
       </c>
       <c r="H88" t="str">
         <f ca="1"/>
-        <v>Robert Dilbeck</v>
+        <v>Rick Bensley</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -4267,7 +4235,7 @@
         <v>783761</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -4284,7 +4252,7 @@
       </c>
       <c r="H89" t="str">
         <f ca="1"/>
-        <v>Ross DeVincentis</v>
+        <v>Roy Collins</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -4292,7 +4260,7 @@
         <v>634821</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>11</v>
@@ -4309,7 +4277,7 @@
       </c>
       <c r="H90" t="str">
         <f ca="1"/>
-        <v>Victor Price</v>
+        <v>Vicky Freymann</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -4317,7 +4285,7 @@
         <v>614225</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>13</v>
@@ -4338,7 +4306,7 @@
         <v>795063</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>16</v>
@@ -4359,7 +4327,7 @@
         <v>682789</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>16</v>
@@ -4380,7 +4348,7 @@
         <v>768339</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>15</v>
@@ -4401,7 +4369,7 @@
         <v>652107</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>16</v>
@@ -4422,7 +4390,7 @@
         <v>796808</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>11</v>
@@ -4443,7 +4411,7 @@
         <v>843427</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>10</v>
@@ -4464,7 +4432,7 @@
         <v>816529</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>16</v>
@@ -4477,7 +4445,7 @@
       </c>
       <c r="F98" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
@@ -4485,7 +4453,7 @@
         <v>682857</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>16</v>
@@ -4506,7 +4474,7 @@
         <v>738532</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>11</v>
@@ -4527,7 +4495,7 @@
         <v>726914</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>16</v>
@@ -4548,7 +4516,7 @@
         <v>817238</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>13</v>
@@ -4569,7 +4537,7 @@
         <v>661311</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>13</v>
@@ -4590,7 +4558,7 @@
         <v>732891</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>15</v>
@@ -4603,14 +4571,14 @@
       </c>
       <c r="F104" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I104" s="2"/>
       <c r="J104" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
@@ -4618,7 +4586,7 @@
         <v>701071</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>11</v>
@@ -4631,11 +4599,11 @@
       </c>
       <c r="F105" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="H105" t="str" cm="1">
-        <f t="array" aca="1" ref="H105:H115" ca="1">_xlfn._xlws.FILTER(Data[Emp Name],TEXT(Data[Date of Admission],"MMM")=TEXT(TODAY(),"MMM"))</f>
-        <v>Adam Hart</v>
+        <f t="array" aca="1" ref="H105:H119" ca="1">_xlfn._xlws.FILTER(Data[Emp Name],TEXT(Data[Date of Admission],"MMM")=TEXT(TODAY(),"MMM"))</f>
+        <v>Tamara Chand</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
@@ -4643,7 +4611,7 @@
         <v>634770</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>13</v>
@@ -4660,7 +4628,7 @@
       </c>
       <c r="H106" t="str">
         <f ca="1"/>
-        <v>Jack O'Briant</v>
+        <v>Jane Waco</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
@@ -4668,7 +4636,7 @@
         <v>831093</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>13</v>
@@ -4685,7 +4653,7 @@
       </c>
       <c r="H107" t="str">
         <f ca="1"/>
-        <v>James Galang</v>
+        <v>Matt Collister</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -4693,7 +4661,7 @@
         <v>747420</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>10</v>
@@ -4710,7 +4678,7 @@
       </c>
       <c r="H108" t="str">
         <f ca="1"/>
-        <v>Janet Martin</v>
+        <v>Michael Paige</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
@@ -4718,7 +4686,7 @@
         <v>662023</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>11</v>
@@ -4735,7 +4703,7 @@
       </c>
       <c r="H109" t="str">
         <f ca="1"/>
-        <v>Maureen Fritzler</v>
+        <v>Mike Gockenbach</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
@@ -4743,7 +4711,7 @@
         <v>832824</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>10</v>
@@ -4760,7 +4728,7 @@
       </c>
       <c r="H110" t="str">
         <f ca="1"/>
-        <v>Max Ludwig</v>
+        <v>Natalie DeCherney</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
@@ -4768,7 +4736,7 @@
         <v>722642</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>12</v>
@@ -4785,7 +4753,7 @@
       </c>
       <c r="H111" t="str">
         <f ca="1"/>
-        <v>Michelle Tran</v>
+        <v>Nick Zandusky</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
@@ -4793,7 +4761,7 @@
         <v>624789</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>15</v>
@@ -4810,7 +4778,7 @@
       </c>
       <c r="H112" t="str">
         <f ca="1"/>
-        <v>Mick Crebagga</v>
+        <v>Nicole Brennan</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -4818,7 +4786,7 @@
         <v>810455</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>16</v>
@@ -4835,7 +4803,7 @@
       </c>
       <c r="H113" t="str">
         <f ca="1"/>
-        <v>Mitch Willingham</v>
+        <v>Richard Eichhorn</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
@@ -4843,7 +4811,7 @@
         <v>811265</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>13</v>
@@ -4860,7 +4828,7 @@
       </c>
       <c r="H114" t="str">
         <f ca="1"/>
-        <v>Rob Haberlin</v>
+        <v>Rick Duston</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4868,7 +4836,7 @@
         <v>725950</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>11</v>
@@ -4885,7 +4853,7 @@
       </c>
       <c r="H115" t="str">
         <f ca="1"/>
-        <v>Rob Lucas</v>
+        <v>Robert Barroso</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
@@ -4893,7 +4861,7 @@
         <v>787011</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>16</v>
@@ -4906,7 +4874,11 @@
       </c>
       <c r="F116" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
+      </c>
+      <c r="H116" t="str">
+        <f ca="1"/>
+        <v>Ryan Crowe</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
@@ -4914,7 +4886,7 @@
         <v>615996</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>10</v>
@@ -4928,6 +4900,10 @@
       <c r="F117" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
         <v>NO</v>
+      </c>
+      <c r="H117" t="str">
+        <f ca="1"/>
+        <v>Valerie Dominguez</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4935,7 +4911,7 @@
         <v>682515</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>15</v>
@@ -4949,6 +4925,10 @@
       <c r="F118" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
         <v>NO</v>
+      </c>
+      <c r="H118" t="str">
+        <f ca="1"/>
+        <v>Valerie Mitchum</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
@@ -4956,7 +4936,7 @@
         <v>704760</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>12</v>
@@ -4970,6 +4950,10 @@
       <c r="F119" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
         <v>NO</v>
+      </c>
+      <c r="H119" t="str">
+        <f ca="1"/>
+        <v>Valerie Takahito</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -4977,7 +4961,7 @@
         <v>847781</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>15</v>
@@ -4998,7 +4982,7 @@
         <v>696828</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>12</v>
@@ -5019,7 +5003,7 @@
         <v>634517</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>13</v>
@@ -5040,7 +5024,7 @@
         <v>742296</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>12</v>
@@ -5053,7 +5037,7 @@
       </c>
       <c r="F123" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
@@ -5061,7 +5045,7 @@
         <v>802572</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>15</v>
@@ -5082,7 +5066,7 @@
         <v>621423</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>13</v>
@@ -5103,7 +5087,7 @@
         <v>763904</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>16</v>
@@ -5124,7 +5108,7 @@
         <v>748868</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>12</v>
@@ -5145,7 +5129,7 @@
         <v>681871</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>13</v>
@@ -5166,7 +5150,7 @@
         <v>632210</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>13</v>
@@ -5187,7 +5171,7 @@
         <v>749547</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>15</v>
@@ -5208,7 +5192,7 @@
         <v>834708</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>11</v>
@@ -5229,7 +5213,7 @@
         <v>817357</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>13</v>
@@ -5242,7 +5226,7 @@
       </c>
       <c r="F132" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -5250,7 +5234,7 @@
         <v>730799</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>16</v>
@@ -5271,7 +5255,7 @@
         <v>693063</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>11</v>
@@ -5292,7 +5276,7 @@
         <v>634332</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>13</v>
@@ -5313,7 +5297,7 @@
         <v>778171</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>10</v>
@@ -5334,7 +5318,7 @@
         <v>651333</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>12</v>
@@ -5355,7 +5339,7 @@
         <v>667971</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>16</v>
@@ -5376,7 +5360,7 @@
         <v>837894</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>10</v>
@@ -5397,7 +5381,7 @@
         <v>716958</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>16</v>
@@ -5418,7 +5402,7 @@
         <v>747513</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>13</v>
@@ -5439,7 +5423,7 @@
         <v>736335</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>13</v>
@@ -5460,7 +5444,7 @@
         <v>796788</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>13</v>
@@ -5481,7 +5465,7 @@
         <v>637345</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>12</v>
@@ -5494,7 +5478,7 @@
       </c>
       <c r="F144" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -5502,7 +5486,7 @@
         <v>760692</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>15</v>
@@ -5515,7 +5499,7 @@
       </c>
       <c r="F145" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -5523,7 +5507,7 @@
         <v>778839</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>10</v>
@@ -5544,7 +5528,7 @@
         <v>616908</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>11</v>
@@ -5565,7 +5549,7 @@
         <v>634844</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>13</v>
@@ -5586,7 +5570,7 @@
         <v>772907</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>12</v>
@@ -5607,7 +5591,7 @@
         <v>724515</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>16</v>
@@ -5628,7 +5612,7 @@
         <v>763589</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>10</v>
@@ -5649,7 +5633,7 @@
         <v>658864</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5654,7 @@
         <v>729275</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>10</v>
@@ -5691,7 +5675,7 @@
         <v>647100</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>10</v>
@@ -5712,7 +5696,7 @@
         <v>822775</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>13</v>
@@ -5725,7 +5709,7 @@
       </c>
       <c r="F155" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -5733,7 +5717,7 @@
         <v>742179</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>12</v>
@@ -5746,7 +5730,7 @@
       </c>
       <c r="F156" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -5754,7 +5738,7 @@
         <v>654559</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>10</v>
@@ -5775,7 +5759,7 @@
         <v>849457</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>12</v>
@@ -5796,7 +5780,7 @@
         <v>771779</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>16</v>
@@ -5817,7 +5801,7 @@
         <v>804242</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>16</v>
@@ -5838,7 +5822,7 @@
         <v>750616</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>15</v>
@@ -5859,7 +5843,7 @@
         <v>812452</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>13</v>
@@ -5880,7 +5864,7 @@
         <v>831582</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>10</v>
@@ -5901,7 +5885,7 @@
         <v>673556</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>13</v>
@@ -5922,7 +5906,7 @@
         <v>674968</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>15</v>
@@ -5943,7 +5927,7 @@
         <v>686386</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>11</v>
@@ -5964,7 +5948,7 @@
         <v>682990</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>12</v>
@@ -5985,7 +5969,7 @@
         <v>726397</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>11</v>
@@ -6006,7 +5990,7 @@
         <v>732402</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>15</v>
@@ -6019,7 +6003,7 @@
       </c>
       <c r="F169" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -6027,7 +6011,7 @@
         <v>636730</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>16</v>
@@ -6040,7 +6024,7 @@
       </c>
       <c r="F170" s="6" t="str">
         <f ca="1">IF(TEXT(TODAY(),"MMM")=TEXT(Data[[#This Row],[Date of Birth]],"MMM"),"YES","NO")</f>
-        <v>YES</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -6048,7 +6032,7 @@
         <v>818442</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>16</v>
@@ -6069,7 +6053,7 @@
         <v>634539</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>17</v>
@@ -6090,7 +6074,7 @@
         <v>663573</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>11</v>
@@ -6111,7 +6095,7 @@
         <v>761270</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>11</v>
@@ -6132,7 +6116,7 @@
         <v>625932</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>10</v>
@@ -6153,7 +6137,7 @@
         <v>846932</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>15</v>
@@ -6174,7 +6158,7 @@
         <v>721677</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>17</v>
@@ -6195,7 +6179,7 @@
         <v>631456</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>13</v>
@@ -6216,7 +6200,7 @@
         <v>704181</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>17</v>
@@ -6237,7 +6221,7 @@
         <v>685127</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>11</v>
@@ -6258,7 +6242,7 @@
         <v>849364</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>17</v>
